--- a/data/trans_camb/IP04D$colectiva-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,27</t>
+          <t>-2,02; 4,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,23; 13,69</t>
+          <t>3,93; 13,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,71</t>
+          <t>-1,89; 2,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 5,61</t>
+          <t>0,19; 5,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,57</t>
+          <t>-1,23; 2,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 8,09</t>
+          <t>3,01; 8,49</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,58; 596,05</t>
+          <t>-71,09; 654,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,64; 2043,39</t>
+          <t>59,86; 2184,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 1177,78</t>
+          <t>-32,44; 1234,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,38; 292,61</t>
+          <t>-53,58; 321,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>86,42; 948,04</t>
+          <t>91,83; 931,39</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,27</t>
+          <t>-5,7; -0,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 7,34</t>
+          <t>-0,63; 7,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,8</t>
+          <t>-4,25; 0,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,5</t>
+          <t>0,72; 6,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,3</t>
+          <t>-3,95; -0,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,77</t>
+          <t>0,8; 5,97</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,49; 21,08</t>
+          <t>-84,32; 15,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 231,86</t>
+          <t>-12,43; 217,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-87,38; 53,79</t>
+          <t>-86,1; 56,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,31; 373,24</t>
+          <t>7,47; 345,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,91; -3,0</t>
+          <t>-77,12; -9,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,39; 203,73</t>
+          <t>14,7; 208,71</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,23</t>
+          <t>-0,69; 4,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,73</t>
+          <t>1,53; 8,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,45</t>
+          <t>-1,47; 3,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,6</t>
+          <t>0,88; 7,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 2,83</t>
+          <t>-0,55; 2,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,8</t>
+          <t>2,1; 6,69</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,67; —</t>
+          <t>-87,17; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,28; —</t>
+          <t>-7,13; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,67; 554,54</t>
+          <t>-74,96; 611,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,48; 1408,17</t>
+          <t>-12,39; 1275,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 423,71</t>
+          <t>-39,28; 451,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78,99; 1029,83</t>
+          <t>95,1; 1079,33</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,59</t>
+          <t>-3,3; 4,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 7,57</t>
+          <t>-1,05; 7,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 8,27</t>
+          <t>-0,14; 8,01</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,73</t>
+          <t>1,71; 11,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 4,8</t>
+          <t>-0,34; 5,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 8,25</t>
+          <t>1,95; 8,33</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,38; 127,82</t>
+          <t>-48,22; 137,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 227,98</t>
+          <t>-21,78; 239,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 299,87</t>
+          <t>-8,56; 325,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25,99; 445,21</t>
+          <t>20,35; 426,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,55; 139,8</t>
+          <t>-11,13; 148,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,14; 255,93</t>
+          <t>29,44; 235,54</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,66</t>
+          <t>-1,6; 1,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,73</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,21</t>
+          <t>-0,69; 2,29</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,01</t>
+          <t>2,38; 6,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,52</t>
+          <t>-0,73; 1,47</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,64</t>
+          <t>2,77; 5,67</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 63,35</t>
+          <t>-36,91; 63,78</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>52,26; 235,81</t>
+          <t>47,36; 232,28</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,99; 97,73</t>
+          <t>-20,63; 107,8</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54,51; 283,88</t>
+          <t>62,03; 279,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,67; 60,75</t>
+          <t>-19,49; 55,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,71; 211,51</t>
+          <t>77,47; 219,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Habitat-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,84</t>
+          <t>-2,29; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 13,93</t>
+          <t>4,31; 13,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 2,68</t>
+          <t>-1,92; 2,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,78</t>
+          <t>0,06; 5,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,67</t>
+          <t>-1,31; 2,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,49</t>
+          <t>2,99; 8,47</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,09; 654,77</t>
+          <t>-73,88; 584,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>59,86; 2184,44</t>
+          <t>91,3; 2129,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,44; 1234,26</t>
+          <t>-18,04; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,58; 321,42</t>
+          <t>-61,95; 354,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,83; 931,39</t>
+          <t>84,05; 969,24</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; -0,03</t>
+          <t>-5,52; 0,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 7,39</t>
+          <t>-0,59; 7,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,78</t>
+          <t>-3,87; 0,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,92</t>
+          <t>0,25; 6,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; -0,35</t>
+          <t>-4,02; -0,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,97</t>
+          <t>0,78; 5,65</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-84,32; 15,4</t>
+          <t>-85,03; 19,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-12,43; 217,16</t>
+          <t>-11,7; 241,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,1; 56,31</t>
+          <t>-86,19; 53,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 345,84</t>
+          <t>-1,56; 335,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,12; -9,67</t>
+          <t>-75,19; 1,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 208,71</t>
+          <t>11,19; 189,5</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,04</t>
+          <t>-0,5; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,19</t>
+          <t>1,47; 8,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,41</t>
+          <t>-1,65; 3,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,79</t>
+          <t>1,16; 7,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,85</t>
+          <t>-0,63; 2,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,69</t>
+          <t>2,22; 6,91</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-87,17; —</t>
+          <t>-69,24; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-7,13; —</t>
+          <t>-4,73; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-74,96; 611,64</t>
+          <t>-76,07; 500,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 1275,93</t>
+          <t>19,79; 1276,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 451,55</t>
+          <t>-41,96; 464,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95,1; 1079,33</t>
+          <t>77,63; 1121,17</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,37</t>
+          <t>-3,04; 4,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 7,97</t>
+          <t>-1,06; 7,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 8,01</t>
+          <t>-0,13; 8,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 11,71</t>
+          <t>1,6; 11,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 5,23</t>
+          <t>-0,47; 5,06</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 8,33</t>
+          <t>1,52; 8,27</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,22; 137,5</t>
+          <t>-44,98; 132,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 239,41</t>
+          <t>-16,23; 226,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 325,38</t>
+          <t>-8,89; 317,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20,35; 426,97</t>
+          <t>11,86; 469,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 148,45</t>
+          <t>-8,66; 144,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,44; 235,54</t>
+          <t>22,47; 227,15</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,7</t>
+          <t>-1,6; 1,81</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,59</t>
+          <t>2,27; 6,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,29</t>
+          <t>-0,65; 2,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,22</t>
+          <t>2,19; 5,91</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,47</t>
+          <t>-0,61; 1,55</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,67</t>
+          <t>2,93; 5,72</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,91; 63,78</t>
+          <t>-36,68; 69,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47,36; 232,28</t>
+          <t>50,18; 236,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 107,8</t>
+          <t>-19,65; 110,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62,03; 279,0</t>
+          <t>60,33; 277,57</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 55,22</t>
+          <t>-17,33; 59,2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,47; 219,1</t>
+          <t>74,45; 210,8</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$colectiva-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$colectiva-Habitat-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que dispone de calefacción colectiva en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,5</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1,17</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,66</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,22</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,6</t>
+          <t>8,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,4</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,4</t>
+          <t>-1,93; 2,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 13,8</t>
+          <t>-0,06; 5,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,65</t>
+          <t>-2,38; 4,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,75</t>
+          <t>4,0; 13,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,74</t>
+          <t>-1,26; 2,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,47</t>
+          <t>2,93; 8,32</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>15,93%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>184,45%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>56,32%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>417,15%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191,52%</t>
+          <t>403,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>315,16%</t>
+          <t>318,3%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,88; 584,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,3; 2129,19</t>
+          <t>-29,05; 1191,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,58; 596,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,04; —</t>
+          <t>60,27; 1987,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,95; 354,18</t>
+          <t>-55,38; 292,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,05; 969,24</t>
+          <t>88,72; 933,95</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,11</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,66</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,18</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 0,16</t>
+          <t>-3,86; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 7,45</t>
+          <t>0,21; 6,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,61</t>
+          <t>-5,48; 0,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,74</t>
+          <t>-0,61; 7,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -0,28</t>
+          <t>-4,03; -0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,65</t>
+          <t>0,82; 5,66</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-50,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-54,86%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>63,58%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-50,2%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110,77%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>78,82%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-85,03; 19,02</t>
+          <t>-87,38; 53,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 241,05</t>
+          <t>-0,27; 347,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,19; 53,8</t>
+          <t>-84,49; 21,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 335,82</t>
+          <t>-14,33; 251,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 1,68</t>
+          <t>-76,91; -3,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 189,5</t>
+          <t>15,24; 197,1</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,63</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>1,51</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,53</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>5,06</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,0</t>
+          <t>-1,56; 3,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,13</t>
+          <t>0,95; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,22</t>
+          <t>-0,71; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,73</t>
+          <t>2,95; 11,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 2,78</t>
+          <t>-0,49; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,91</t>
+          <t>2,94; 7,88</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>41,3%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>271,57%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>160,73%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>481,01%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41,3%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256,71%</t>
+          <t>642,86%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>339,15%</t>
+          <t>407,74%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-69,24; —</t>
+          <t>-76,67; 554,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,73; —</t>
+          <t>6,25; 1561,59</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,07; 500,86</t>
+          <t>-73,67; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19,79; 1276,06</t>
+          <t>13,54; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 464,6</t>
+          <t>-42,4; 423,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,63; 1121,17</t>
+          <t>111,37; 1168,04</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,39</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>3,39</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3,92</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,47</t>
+          <t>3,43</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,97</t>
+          <t>4,91</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,4</t>
+          <t>0,02; 8,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,73</t>
+          <t>2,19; 11,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 8,03</t>
+          <t>-3,05; 4,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 11,58</t>
+          <t>-0,9; 7,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 5,06</t>
+          <t>-0,68; 4,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 8,27</t>
+          <t>1,73; 8,33</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>148,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>12,39%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>67,07%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>150,65%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>106,33%</t>
+          <t>105,12%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 132,58</t>
+          <t>-6,14; 299,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 226,4</t>
+          <t>25,69; 445,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 317,49</t>
+          <t>-45,38; 127,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,86; 469,94</t>
+          <t>-19,17; 229,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 144,33</t>
+          <t>-12,55; 139,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,47; 227,15</t>
+          <t>26,88; 253,73</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4,01</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,03</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,75</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,92</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,22</t>
+          <t>4,43</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,81</t>
+          <t>-0,88; 2,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,56</t>
+          <t>2,1; 5,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,25</t>
+          <t>-1,47; 1,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,91</t>
+          <t>2,84; 7,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,55</t>
+          <t>-0,79; 1,52</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,72</t>
+          <t>3,05; 5,84</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,03%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>143,91%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-0,99%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>123,79%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>27,03%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>148,91%</t>
+          <t>140,44%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>134,77%</t>
+          <t>141,43%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 69,46</t>
+          <t>-26,99; 97,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>50,18; 236,95</t>
+          <t>53,57; 282,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,65; 110,08</t>
+          <t>-36,12; 63,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>60,33; 277,57</t>
+          <t>65,51; 258,1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 59,2</t>
+          <t>-21,67; 60,75</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,45; 210,8</t>
+          <t>79,73; 221,19</t>
         </is>
       </c>
     </row>
